--- a/docs/規格書/檔案位子範例/config/application.xlsx
+++ b/docs/規格書/檔案位子範例/config/application.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64cd5bb3604bb353/Desktop/共保志工險/規格書/檔案位子範例/confog/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\Health-and-Injury-Co-Insurance-System\docs\規格書\檔案位子範例\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="11_AD4DBB64A54DDB1B405E389605D904C94E90DF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87A7405A-8495-418A-9E91-EF347E8B46A9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAC9C02-C305-415B-AD4E-A58B781DF748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-8370" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -831,7 +831,7 @@
         <v>31</v>
       </c>
       <c r="C13" s="4">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D13" s="11"/>
       <c r="F13" s="12"/>

--- a/docs/規格書/檔案位子範例/config/application.xlsx
+++ b/docs/規格書/檔案位子範例/config/application.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\Health-and-Injury-Co-Insurance-System\docs\規格書\檔案位子範例\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\Health-and-Injury-Co-Insurance-System\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAC9C02-C305-415B-AD4E-A58B781DF748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494EE3AF-386F-471F-A45B-2D0E613C2F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-8370" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -169,6 +169,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -310,7 +313,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -346,6 +349,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -667,11 +673,11 @@
     </row>
     <row r="3" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="16"/>
       <c r="K4" s="8"/>
       <c r="L4" s="9"/>
       <c r="M4" s="10"/>
@@ -703,8 +709,8 @@
       <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4">
-        <v>0.05</v>
+      <c r="C6" s="13">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D6" s="11"/>
       <c r="F6" s="12"/>
@@ -722,8 +728,8 @@
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4">
-        <v>0.05</v>
+      <c r="C7" s="13">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D7" s="11"/>
       <c r="F7" s="12"/>
@@ -741,8 +747,8 @@
       <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="4">
-        <v>0.05</v>
+      <c r="C8" s="13">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D8" s="11"/>
       <c r="F8" s="12"/>
@@ -760,8 +766,8 @@
       <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="4">
-        <v>0.1</v>
+      <c r="C9" s="13">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D9" s="11"/>
       <c r="F9" s="12"/>
@@ -779,8 +785,8 @@
       <c r="B10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="4">
-        <v>0.1</v>
+      <c r="C10" s="13">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D10" s="11"/>
       <c r="F10" s="12"/>
@@ -798,8 +804,8 @@
       <c r="B11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="4">
-        <v>0.1</v>
+      <c r="C11" s="13">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D11" s="11"/>
       <c r="F11" s="12"/>
@@ -817,8 +823,8 @@
       <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="4">
-        <v>0.05</v>
+      <c r="C12" s="13">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D12" s="11"/>
       <c r="F12" s="12"/>
@@ -830,8 +836,8 @@
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="4">
-        <v>0.05</v>
+      <c r="C13" s="13">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D13" s="11"/>
       <c r="F13" s="12"/>
@@ -844,7 +850,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="4">
-        <v>0.12</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
